--- a/public/exports-from-60-with-coowners/29189897.xlsx
+++ b/public/exports-from-60-with-coowners/29189897.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -31639,7 +31639,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769950</t>
+          <t xml:space="preserve">311769954</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -32014,7 +32014,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769950</t>
+          <t xml:space="preserve">311769954</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189897.xlsx
+++ b/public/exports-from-60-with-coowners/29189897.xlsx
@@ -31639,7 +31639,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769954</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -31789,7 +31789,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769950</t>
+          <t xml:space="preserve">311769953</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -32014,7 +32014,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769954</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -34114,7 +34114,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824278</t>
+          <t xml:space="preserve">311824283</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189897.xlsx
+++ b/public/exports-from-60-with-coowners/29189897.xlsx
@@ -31789,7 +31789,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769953</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Mosevej 37</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -32301,30 +32301,30 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5023541</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J431">
-        <v>1613</v>
+        <v>1328</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311787606</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -32351,12 +32351,12 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolding Kommune</t>
+          <t xml:space="preserve">OMJ Ejendomme, Kolding ApS</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Toldbodgade 10</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -32376,30 +32376,30 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">328041, 328044, 328045, 328046, 328047</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J432">
-        <v>486</v>
+        <v>5696</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311800098</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-11-28</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -32426,12 +32426,12 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolding Kommune</t>
+          <t xml:space="preserve">ARBEJDERNES ANDELSBOLIGFORENING</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Ny Vestergade 2</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -32451,30 +32451,30 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">327203, 327204, 327205, 327206, 327207</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J433">
-        <v>540</v>
+        <v>3246</v>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311802497</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -32516,40 +32516,40 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Bagvejen 1</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6064</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5023161</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J434">
-        <v>428</v>
+        <v>117</v>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818306</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -32591,40 +32591,40 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Bagvejen 3</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6064</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5023161</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J435">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818305</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -32666,40 +32666,40 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Hjarupvej 14</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6640</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5027423</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J436">
-        <v>2260</v>
+        <v>4461</v>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818310</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -32741,40 +32741,40 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Hjarupvej 14</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6640</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5027423</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J437">
-        <v>1303</v>
+        <v>96</v>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818307</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">W. Kiørboes Vej 3</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -32826,30 +32826,30 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7524697</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J438">
-        <v>253</v>
+        <v>825</v>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311820661</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -32891,40 +32891,40 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Vesterled 1</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J439">
-        <v>562</v>
+        <v>742</v>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311824146</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -32966,40 +32966,40 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Ødis Byvej 6</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J440">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311823954</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -33041,40 +33041,40 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Ødis Byvej 6</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J441">
-        <v>92</v>
+        <v>1337</v>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311824146</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -33116,7 +33116,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Esbjergvej 108</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -33126,30 +33126,30 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">4387067</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J442">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311824278</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -33191,7 +33191,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannersvej 4</t>
+          <t xml:space="preserve">Skovvejen 1A</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -33201,30 +33201,30 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5681097</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J443">
-        <v>2917</v>
+        <v>982</v>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311826209</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 37</t>
+          <t xml:space="preserve">Skovvejen 1B</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -33276,30 +33276,30 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023541</t>
+          <t xml:space="preserve">5681097</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J444">
-        <v>1328</v>
+        <v>1766</v>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787606</t>
+          <t xml:space="preserve">311826212</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -33326,12 +33326,12 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMJ Ejendomme, Kolding ApS</t>
+          <t xml:space="preserve">Kolding Kommune</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -33341,40 +33341,40 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toldbodgade 10</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">328041, 328044, 328045, 328046, 328047</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J445">
-        <v>5696</v>
+        <v>2848</v>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800098</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-28</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -33401,12 +33401,12 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARBEJDERNES ANDELSBOLIGFORENING</t>
+          <t xml:space="preserve">Kolding Kommune</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -33416,40 +33416,40 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Vestergade 2</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">327203, 327204, 327205, 327206, 327207</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J446">
-        <v>3246</v>
+        <v>1172</v>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802497</t>
+          <t xml:space="preserve">311826644</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-13</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -33491,30 +33491,30 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvejen 1</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t xml:space="preserve">6064</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023161</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J447">
-        <v>117</v>
+        <v>2017</v>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818306</t>
+          <t xml:space="preserve">311826644</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -33524,7 +33524,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -33566,30 +33566,30 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvejen 3</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t xml:space="preserve">6064</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023161</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J448">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818305</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -33599,7 +33599,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -33641,30 +33641,30 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjarupvej 14</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t xml:space="preserve">6640</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027423</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J449">
-        <v>4461</v>
+        <v>218</v>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818310</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
@@ -33674,7 +33674,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -33716,30 +33716,30 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjarupvej 14</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t xml:space="preserve">6640</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027423</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J450">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818307</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -33749,7 +33749,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -33791,40 +33791,40 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t xml:space="preserve">W. Kiørboes Vej 3</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">7524697</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J451">
-        <v>825</v>
+        <v>100</v>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820661</t>
+          <t xml:space="preserve">311826641</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-27</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 1</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -33876,20 +33876,20 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J452">
-        <v>742</v>
+        <v>803</v>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824146</t>
+          <t xml:space="preserve">311826644</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -33941,7 +33941,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ødis Byvej 6</t>
+          <t xml:space="preserve">Herredsvej 45B</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -33951,20 +33951,20 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J453">
-        <v>542</v>
+        <v>371</v>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823954</t>
+          <t xml:space="preserve">311826639</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -34016,30 +34016,30 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ødis Byvej 6</t>
+          <t xml:space="preserve">Sjølund Gade 28</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6093</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">5069465</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J454">
-        <v>1337</v>
+        <v>1387</v>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824146</t>
+          <t xml:space="preserve">311827156</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -34091,7 +34091,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esbjergvej 108</t>
+          <t xml:space="preserve">Hjarupvej 10</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -34101,20 +34101,20 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387067</t>
+          <t xml:space="preserve">5069995</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J455">
-        <v>320</v>
+        <v>5886</v>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824283</t>
+          <t xml:space="preserve">311828899</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -34124,7 +34124,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-05-02</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -34166,30 +34166,30 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 1A</t>
+          <t xml:space="preserve">Birkevej 9A</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681097</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J456">
-        <v>982</v>
+        <v>361</v>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826209</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -34199,7 +34199,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-22</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -34241,30 +34241,30 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 1B</t>
+          <t xml:space="preserve">Birkevej 9A</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681097</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J457">
-        <v>1766</v>
+        <v>525</v>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826212</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -34274,7 +34274,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-22</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -34316,30 +34316,30 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Birkevej 9A</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J458">
-        <v>2848</v>
+        <v>93</v>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -34349,7 +34349,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -34391,30 +34391,30 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Ågade 27</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">9218207</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J459">
-        <v>1172</v>
+        <v>5961</v>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311832620</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -34424,7 +34424,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Idrætsvej 1A</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -34476,20 +34476,20 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5028587</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J460">
-        <v>2017</v>
+        <v>3079</v>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311833037</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -34541,17 +34541,17 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Rytterskolevej 15</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">10170544</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -34560,11 +34560,11 @@
         </is>
       </c>
       <c r="J461">
-        <v>130</v>
+        <v>636</v>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311834137</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -34574,7 +34574,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-05-25</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -34616,30 +34616,30 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Seestvej 10</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">100068900</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J462">
-        <v>218</v>
+        <v>1983</v>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311837586</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -34691,30 +34691,30 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Brostræde 3</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">8761653</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J463">
-        <v>218</v>
+        <v>1713</v>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826640</t>
+          <t xml:space="preserve">311839054</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -34724,7 +34724,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -34766,30 +34766,30 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Brostræde 3A</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">8761653</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J464">
-        <v>100</v>
+        <v>4121</v>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826641</t>
+          <t xml:space="preserve">311839051</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -34841,30 +34841,30 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Birkevej 24</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">304880, 304881</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J465">
-        <v>803</v>
+        <v>2656</v>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311841720</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-30</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -34916,40 +34916,40 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45B</t>
+          <t xml:space="preserve">Bredgade 1</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5675450</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J466">
-        <v>371</v>
+        <v>2112</v>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826639</t>
+          <t xml:space="preserve">311844296</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -34991,17 +34991,17 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjølund Gade 28</t>
+          <t xml:space="preserve">Kongensgade 34A</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t xml:space="preserve">6093</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069465</t>
+          <t xml:space="preserve">5766969</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -35010,11 +35010,11 @@
         </is>
       </c>
       <c r="J467">
-        <v>1387</v>
+        <v>2092</v>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827156</t>
+          <t xml:space="preserve">311847624</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-08-06</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -35066,7 +35066,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjarupvej 10</t>
+          <t xml:space="preserve">Ved Padholm 2</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -35076,30 +35076,30 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069995</t>
+          <t xml:space="preserve">100497241</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J468">
-        <v>5886</v>
+        <v>1865</v>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828899</t>
+          <t xml:space="preserve">311861662</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-02</t>
+          <t xml:space="preserve">2035-10-13</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -35141,17 +35141,17 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 9A</t>
+          <t xml:space="preserve">Zahnsgade 12</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">5676445</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -35160,21 +35160,21 @@
         </is>
       </c>
       <c r="J469">
-        <v>361</v>
+        <v>195</v>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311868470</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-11-16</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -35216,40 +35216,40 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 9A</t>
+          <t xml:space="preserve">Kobbervej 14</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">100643290</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J470">
-        <v>525</v>
+        <v>711</v>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311869504</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -35291,17 +35291,17 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 9A</t>
+          <t xml:space="preserve">Kobbervej 14</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">100643290</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -35310,21 +35310,21 @@
         </is>
       </c>
       <c r="J471">
-        <v>93</v>
+        <v>307</v>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311869505</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 27</t>
+          <t xml:space="preserve">Stadionvej 11</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -35376,30 +35376,30 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218207</t>
+          <t xml:space="preserve">100891244, 100891245</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J472">
-        <v>5961</v>
+        <v>5997</v>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832620</t>
+          <t xml:space="preserve">311871668</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -35441,17 +35441,17 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1A</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">5028587</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -35460,21 +35460,21 @@
         </is>
       </c>
       <c r="J473">
-        <v>3079</v>
+        <v>1613</v>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833037</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterskolevej 15</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -35526,30 +35526,30 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">10170544</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J474">
-        <v>636</v>
+        <v>486</v>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834137</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-25</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -35591,7 +35591,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seestvej 10</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -35601,30 +35601,30 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">100068900</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J475">
-        <v>1983</v>
+        <v>540</v>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837586</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-12</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brostræde 3</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -35676,30 +35676,30 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761653</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J476">
-        <v>1713</v>
+        <v>428</v>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839054</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -35741,7 +35741,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brostræde 3A</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -35751,30 +35751,30 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761653</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J477">
-        <v>4121</v>
+        <v>96</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839051</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -35816,40 +35816,40 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 24</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">304880, 304881</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J478">
-        <v>2656</v>
+        <v>2260</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841720</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-30</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 1</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -35901,30 +35901,30 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675450</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J479">
-        <v>2112</v>
+        <v>1303</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844296</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-11</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -35966,40 +35966,40 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 34A</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766969</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J480">
-        <v>2092</v>
+        <v>253</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847624</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-06</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -36041,7 +36041,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Padholm 2</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -36051,30 +36051,30 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">100497241</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J481">
-        <v>1865</v>
+        <v>562</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861662</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-13</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zahnsgade 12</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -36126,30 +36126,30 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">5676445</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J482">
-        <v>195</v>
+        <v>505</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868470</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-16</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -36191,7 +36191,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbervej 14</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -36201,30 +36201,30 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">100643290</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J483">
-        <v>711</v>
+        <v>92</v>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869504</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbervej 14</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -36276,30 +36276,30 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">100643290</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J484">
-        <v>307</v>
+        <v>380</v>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869505</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -36341,7 +36341,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 11</t>
+          <t xml:space="preserve">Dannersvej 4</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -36351,30 +36351,30 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">100891244, 100891245</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J485">
-        <v>5997</v>
+        <v>2917</v>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871668</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbjerg Energimærkning</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
